--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PA/BOM_PA.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_PA/BOM_PA.xlsx
@@ -664,7 +664,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C1, C4, C5</t>
+          <t>C1, C4, C5, C10, C11, C12, C13, C14, C15, C16, C17, C10, C11, C12, C13, C14, C15, C16, C17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
